--- a/dataset/Faulty/return_local.xlsx
+++ b/dataset/Faulty/return_local.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/return_local.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/return_local.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/return_local.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/return_local.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
